--- a/data/ams_weekly_data/Audio_Array/ads_report_week10.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\ams_weekly_data\Audio_Array\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B2865A-E1C0-41E1-9DE9-B23988023D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F51F2D-E6B0-4A16-BF74-2C775041DF66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{C2EB3544-0B30-4B5A-9817-98DE85FBF6BC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C2EB3544-0B30-4B5A-9817-98DE85FBF6BC}"/>
   </bookViews>
   <sheets>
     <sheet name="SP" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10247" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10683" uniqueCount="319">
   <si>
     <t>Brand</t>
   </si>
@@ -953,6 +953,54 @@
   <si>
     <t>Audio Array</t>
   </si>
+  <si>
+    <t>AA_DJ Headphone_AH-50_SBV_CT &amp; PT</t>
+  </si>
+  <si>
+    <t>AA_DJ Headphone_AH-50_SBV_CT &amp; PT - Portrait</t>
+  </si>
+  <si>
+    <t>AA_Condenser_AM-C1_SB_PT</t>
+  </si>
+  <si>
+    <t>AA_Audio_Interface_AI-04 Red_SBV_CT&amp;PT</t>
+  </si>
+  <si>
+    <t>AA_Conference_AM-W45_SBV_KT</t>
+  </si>
+  <si>
+    <t>AA_Speaker_Karaoke_AM-W18_SBV_CT&amp;PT</t>
+  </si>
+  <si>
+    <t>AA_Studio_Monitor_AM-S1_SBV_KT</t>
+  </si>
+  <si>
+    <t>AA_Studio_Monitor_AM-S1_SBV_CT</t>
+  </si>
+  <si>
+    <t>AA_Condenser_AM-C46_SBV_KT</t>
+  </si>
+  <si>
+    <t>AA_Dynamic_AM-C45_SBV_KT</t>
+  </si>
+  <si>
+    <t>Audio Array AM-C44 SBV KT - B0CM9KJZWQ</t>
+  </si>
+  <si>
+    <t>AA_Condenser_AM-C47_SBV_KT</t>
+  </si>
+  <si>
+    <t>AA_WL_AM-W22_SBV_KT</t>
+  </si>
+  <si>
+    <t>AA_Condenser_AM-C1_SBV_KT</t>
+  </si>
+  <si>
+    <t>AA__All_Products_SB</t>
+  </si>
+  <si>
+    <t>AA__Accessories_SB_PT</t>
+  </si>
 </sst>
 </file>
 
@@ -1322,7 +1370,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51EF6D63-3663-4E20-A7FC-263D078FDDB8}">
-  <dimension ref="A1:I2173"/>
+  <dimension ref="A1:I2282"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21.88671875" customWidth="1"/>
@@ -64342,6 +64390,3167 @@
         <v>0</v>
       </c>
       <c r="I2173" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2174" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2174" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2174" t="s">
+        <v>303</v>
+      </c>
+      <c r="C2174" t="s">
+        <v>253</v>
+      </c>
+      <c r="D2174">
+        <v>1234</v>
+      </c>
+      <c r="E2174">
+        <v>5</v>
+      </c>
+      <c r="F2174">
+        <v>67.27</v>
+      </c>
+      <c r="G2174">
+        <v>0</v>
+      </c>
+      <c r="H2174">
+        <v>0</v>
+      </c>
+      <c r="I2174" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2175" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2175" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2175" t="s">
+        <v>303</v>
+      </c>
+      <c r="C2175" t="s">
+        <v>253</v>
+      </c>
+      <c r="D2175">
+        <v>1898</v>
+      </c>
+      <c r="E2175">
+        <v>1</v>
+      </c>
+      <c r="F2175">
+        <v>20.22</v>
+      </c>
+      <c r="G2175">
+        <v>0</v>
+      </c>
+      <c r="H2175">
+        <v>0</v>
+      </c>
+      <c r="I2175" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2176" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2176" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2176" t="s">
+        <v>303</v>
+      </c>
+      <c r="C2176" t="s">
+        <v>253</v>
+      </c>
+      <c r="D2176">
+        <v>2504</v>
+      </c>
+      <c r="E2176">
+        <v>9</v>
+      </c>
+      <c r="F2176">
+        <v>163.93</v>
+      </c>
+      <c r="G2176">
+        <v>0</v>
+      </c>
+      <c r="H2176">
+        <v>0</v>
+      </c>
+      <c r="I2176" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2177" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2177" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2177" t="s">
+        <v>303</v>
+      </c>
+      <c r="C2177" t="s">
+        <v>253</v>
+      </c>
+      <c r="D2177">
+        <v>2035</v>
+      </c>
+      <c r="E2177">
+        <v>7</v>
+      </c>
+      <c r="F2177">
+        <v>104.38</v>
+      </c>
+      <c r="G2177">
+        <v>0</v>
+      </c>
+      <c r="H2177">
+        <v>0</v>
+      </c>
+      <c r="I2177" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2178" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2178" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2178" t="s">
+        <v>303</v>
+      </c>
+      <c r="C2178" t="s">
+        <v>253</v>
+      </c>
+      <c r="D2178">
+        <v>2674</v>
+      </c>
+      <c r="E2178">
+        <v>18</v>
+      </c>
+      <c r="F2178">
+        <v>294.01</v>
+      </c>
+      <c r="G2178">
+        <v>0</v>
+      </c>
+      <c r="H2178">
+        <v>0</v>
+      </c>
+      <c r="I2178" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2179" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2179" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2179" t="s">
+        <v>303</v>
+      </c>
+      <c r="C2179" t="s">
+        <v>253</v>
+      </c>
+      <c r="D2179">
+        <v>2652</v>
+      </c>
+      <c r="E2179">
+        <v>19</v>
+      </c>
+      <c r="F2179">
+        <v>367.38</v>
+      </c>
+      <c r="G2179">
+        <v>0</v>
+      </c>
+      <c r="H2179">
+        <v>0</v>
+      </c>
+      <c r="I2179" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2180" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2180" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2180" t="s">
+        <v>303</v>
+      </c>
+      <c r="C2180" t="s">
+        <v>253</v>
+      </c>
+      <c r="D2180">
+        <v>2962</v>
+      </c>
+      <c r="E2180">
+        <v>18</v>
+      </c>
+      <c r="F2180">
+        <v>311.55</v>
+      </c>
+      <c r="G2180">
+        <v>0</v>
+      </c>
+      <c r="H2180">
+        <v>0</v>
+      </c>
+      <c r="I2180" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2181" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2181" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2181" t="s">
+        <v>304</v>
+      </c>
+      <c r="C2181" t="s">
+        <v>253</v>
+      </c>
+      <c r="D2181">
+        <v>247</v>
+      </c>
+      <c r="E2181">
+        <v>4</v>
+      </c>
+      <c r="F2181">
+        <v>59.14</v>
+      </c>
+      <c r="G2181">
+        <v>0</v>
+      </c>
+      <c r="H2181">
+        <v>0</v>
+      </c>
+      <c r="I2181" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2182" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2182" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2182" t="s">
+        <v>304</v>
+      </c>
+      <c r="C2182" t="s">
+        <v>253</v>
+      </c>
+      <c r="D2182">
+        <v>307</v>
+      </c>
+      <c r="E2182">
+        <v>1</v>
+      </c>
+      <c r="F2182">
+        <v>10.71</v>
+      </c>
+      <c r="G2182">
+        <v>0</v>
+      </c>
+      <c r="H2182">
+        <v>0</v>
+      </c>
+      <c r="I2182" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2183" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2183" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2183" t="s">
+        <v>304</v>
+      </c>
+      <c r="C2183" t="s">
+        <v>253</v>
+      </c>
+      <c r="D2183">
+        <v>197</v>
+      </c>
+      <c r="E2183">
+        <v>4</v>
+      </c>
+      <c r="F2183">
+        <v>70.42</v>
+      </c>
+      <c r="G2183">
+        <v>0</v>
+      </c>
+      <c r="H2183">
+        <v>0</v>
+      </c>
+      <c r="I2183" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2184" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2184" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2184" t="s">
+        <v>304</v>
+      </c>
+      <c r="C2184" t="s">
+        <v>253</v>
+      </c>
+      <c r="D2184">
+        <v>283</v>
+      </c>
+      <c r="E2184">
+        <v>4</v>
+      </c>
+      <c r="F2184">
+        <v>69</v>
+      </c>
+      <c r="G2184">
+        <v>0</v>
+      </c>
+      <c r="H2184">
+        <v>0</v>
+      </c>
+      <c r="I2184" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2185" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2185" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2185" t="s">
+        <v>304</v>
+      </c>
+      <c r="C2185" t="s">
+        <v>253</v>
+      </c>
+      <c r="D2185">
+        <v>103</v>
+      </c>
+      <c r="E2185">
+        <v>2</v>
+      </c>
+      <c r="F2185">
+        <v>32.54</v>
+      </c>
+      <c r="G2185">
+        <v>0</v>
+      </c>
+      <c r="H2185">
+        <v>0</v>
+      </c>
+      <c r="I2185" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2186" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2186" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2186" t="s">
+        <v>304</v>
+      </c>
+      <c r="C2186" t="s">
+        <v>253</v>
+      </c>
+      <c r="D2186">
+        <v>114</v>
+      </c>
+      <c r="E2186">
+        <v>2</v>
+      </c>
+      <c r="F2186">
+        <v>31.26</v>
+      </c>
+      <c r="G2186">
+        <v>0</v>
+      </c>
+      <c r="H2186">
+        <v>0</v>
+      </c>
+      <c r="I2186" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2187" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2187" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2187" t="s">
+        <v>304</v>
+      </c>
+      <c r="C2187" t="s">
+        <v>253</v>
+      </c>
+      <c r="D2187">
+        <v>137</v>
+      </c>
+      <c r="E2187">
+        <v>0</v>
+      </c>
+      <c r="F2187">
+        <v>0</v>
+      </c>
+      <c r="G2187">
+        <v>0</v>
+      </c>
+      <c r="H2187">
+        <v>0</v>
+      </c>
+      <c r="I2187" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2188" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2188" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2188" t="s">
+        <v>305</v>
+      </c>
+      <c r="C2188" t="s">
+        <v>193</v>
+      </c>
+      <c r="D2188">
+        <v>4315</v>
+      </c>
+      <c r="E2188">
+        <v>15</v>
+      </c>
+      <c r="F2188">
+        <v>74.73</v>
+      </c>
+      <c r="G2188">
+        <v>0</v>
+      </c>
+      <c r="H2188">
+        <v>0</v>
+      </c>
+      <c r="I2188" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2189" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2189" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2189" t="s">
+        <v>305</v>
+      </c>
+      <c r="C2189" t="s">
+        <v>193</v>
+      </c>
+      <c r="D2189">
+        <v>4492</v>
+      </c>
+      <c r="E2189">
+        <v>11</v>
+      </c>
+      <c r="F2189">
+        <v>45.72</v>
+      </c>
+      <c r="G2189">
+        <v>0</v>
+      </c>
+      <c r="H2189">
+        <v>0</v>
+      </c>
+      <c r="I2189" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2190" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2190" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2190" t="s">
+        <v>305</v>
+      </c>
+      <c r="C2190" t="s">
+        <v>193</v>
+      </c>
+      <c r="D2190">
+        <v>13940</v>
+      </c>
+      <c r="E2190">
+        <v>54</v>
+      </c>
+      <c r="F2190">
+        <v>437.58</v>
+      </c>
+      <c r="G2190">
+        <v>4447.46</v>
+      </c>
+      <c r="H2190">
+        <v>2</v>
+      </c>
+      <c r="I2190" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2191" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2191" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2191" t="s">
+        <v>305</v>
+      </c>
+      <c r="C2191" t="s">
+        <v>193</v>
+      </c>
+      <c r="D2191">
+        <v>9244</v>
+      </c>
+      <c r="E2191">
+        <v>33</v>
+      </c>
+      <c r="F2191">
+        <v>255.42</v>
+      </c>
+      <c r="G2191">
+        <v>0</v>
+      </c>
+      <c r="H2191">
+        <v>0</v>
+      </c>
+      <c r="I2191" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2192" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2192" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2192" t="s">
+        <v>305</v>
+      </c>
+      <c r="C2192" t="s">
+        <v>193</v>
+      </c>
+      <c r="D2192">
+        <v>8364</v>
+      </c>
+      <c r="E2192">
+        <v>32</v>
+      </c>
+      <c r="F2192">
+        <v>238.67</v>
+      </c>
+      <c r="G2192">
+        <v>0</v>
+      </c>
+      <c r="H2192">
+        <v>0</v>
+      </c>
+      <c r="I2192" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2193" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2193" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2193" t="s">
+        <v>305</v>
+      </c>
+      <c r="C2193" t="s">
+        <v>193</v>
+      </c>
+      <c r="D2193">
+        <v>7133</v>
+      </c>
+      <c r="E2193">
+        <v>39</v>
+      </c>
+      <c r="F2193">
+        <v>376.21</v>
+      </c>
+      <c r="G2193">
+        <v>0</v>
+      </c>
+      <c r="H2193">
+        <v>0</v>
+      </c>
+      <c r="I2193" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2194" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2194" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2194" t="s">
+        <v>305</v>
+      </c>
+      <c r="C2194" t="s">
+        <v>193</v>
+      </c>
+      <c r="D2194">
+        <v>14788</v>
+      </c>
+      <c r="E2194">
+        <v>49</v>
+      </c>
+      <c r="F2194">
+        <v>341.06</v>
+      </c>
+      <c r="G2194">
+        <v>2244.92</v>
+      </c>
+      <c r="H2194">
+        <v>1</v>
+      </c>
+      <c r="I2194" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2195" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2195" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2195" t="s">
+        <v>306</v>
+      </c>
+      <c r="C2195" t="s">
+        <v>194</v>
+      </c>
+      <c r="D2195">
+        <v>11632</v>
+      </c>
+      <c r="E2195">
+        <v>110</v>
+      </c>
+      <c r="F2195">
+        <v>873.73</v>
+      </c>
+      <c r="G2195">
+        <v>0</v>
+      </c>
+      <c r="H2195">
+        <v>0</v>
+      </c>
+      <c r="I2195" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2196" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2196" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2196" t="s">
+        <v>306</v>
+      </c>
+      <c r="C2196" t="s">
+        <v>194</v>
+      </c>
+      <c r="D2196">
+        <v>10879</v>
+      </c>
+      <c r="E2196">
+        <v>89</v>
+      </c>
+      <c r="F2196">
+        <v>671.12</v>
+      </c>
+      <c r="G2196">
+        <v>4024.58</v>
+      </c>
+      <c r="H2196">
+        <v>1</v>
+      </c>
+      <c r="I2196" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2197" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2197" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2197" t="s">
+        <v>306</v>
+      </c>
+      <c r="C2197" t="s">
+        <v>194</v>
+      </c>
+      <c r="D2197">
+        <v>12146</v>
+      </c>
+      <c r="E2197">
+        <v>131</v>
+      </c>
+      <c r="F2197">
+        <v>927.86</v>
+      </c>
+      <c r="G2197">
+        <v>12073.74</v>
+      </c>
+      <c r="H2197">
+        <v>3</v>
+      </c>
+      <c r="I2197" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2198" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2198" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2198" t="s">
+        <v>306</v>
+      </c>
+      <c r="C2198" t="s">
+        <v>194</v>
+      </c>
+      <c r="D2198">
+        <v>11241</v>
+      </c>
+      <c r="E2198">
+        <v>114</v>
+      </c>
+      <c r="F2198">
+        <v>998.59999999999991</v>
+      </c>
+      <c r="G2198">
+        <v>0</v>
+      </c>
+      <c r="H2198">
+        <v>0</v>
+      </c>
+      <c r="I2198" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2199" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2199" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2199" t="s">
+        <v>306</v>
+      </c>
+      <c r="C2199" t="s">
+        <v>194</v>
+      </c>
+      <c r="D2199">
+        <v>11326</v>
+      </c>
+      <c r="E2199">
+        <v>106</v>
+      </c>
+      <c r="F2199">
+        <v>1220.6499999999999</v>
+      </c>
+      <c r="G2199">
+        <v>3982.2</v>
+      </c>
+      <c r="H2199">
+        <v>1</v>
+      </c>
+      <c r="I2199" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2200" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2200" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2200" t="s">
+        <v>306</v>
+      </c>
+      <c r="C2200" t="s">
+        <v>194</v>
+      </c>
+      <c r="D2200">
+        <v>10821</v>
+      </c>
+      <c r="E2200">
+        <v>119</v>
+      </c>
+      <c r="F2200">
+        <v>1729.23</v>
+      </c>
+      <c r="G2200">
+        <v>3982.2</v>
+      </c>
+      <c r="H2200">
+        <v>1</v>
+      </c>
+      <c r="I2200" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2201" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2201" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2201" t="s">
+        <v>306</v>
+      </c>
+      <c r="C2201" t="s">
+        <v>194</v>
+      </c>
+      <c r="D2201">
+        <v>10964</v>
+      </c>
+      <c r="E2201">
+        <v>109</v>
+      </c>
+      <c r="F2201">
+        <v>1720.1399999999999</v>
+      </c>
+      <c r="G2201">
+        <v>3982.2</v>
+      </c>
+      <c r="H2201">
+        <v>1</v>
+      </c>
+      <c r="I2201" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2202" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2202" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2202" t="s">
+        <v>307</v>
+      </c>
+      <c r="C2202" t="s">
+        <v>209</v>
+      </c>
+      <c r="D2202">
+        <v>3092</v>
+      </c>
+      <c r="E2202">
+        <v>12</v>
+      </c>
+      <c r="F2202">
+        <v>139.80000000000001</v>
+      </c>
+      <c r="G2202">
+        <v>0</v>
+      </c>
+      <c r="H2202">
+        <v>0</v>
+      </c>
+      <c r="I2202" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2203" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2203" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2203" t="s">
+        <v>307</v>
+      </c>
+      <c r="C2203" t="s">
+        <v>209</v>
+      </c>
+      <c r="D2203">
+        <v>4060</v>
+      </c>
+      <c r="E2203">
+        <v>24</v>
+      </c>
+      <c r="F2203">
+        <v>289.77999999999997</v>
+      </c>
+      <c r="G2203">
+        <v>4321.1899999999996</v>
+      </c>
+      <c r="H2203">
+        <v>1</v>
+      </c>
+      <c r="I2203" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2204" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2204" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2204" t="s">
+        <v>307</v>
+      </c>
+      <c r="C2204" t="s">
+        <v>209</v>
+      </c>
+      <c r="D2204">
+        <v>2418</v>
+      </c>
+      <c r="E2204">
+        <v>16</v>
+      </c>
+      <c r="F2204">
+        <v>182.91</v>
+      </c>
+      <c r="G2204">
+        <v>0</v>
+      </c>
+      <c r="H2204">
+        <v>0</v>
+      </c>
+      <c r="I2204" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2205" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2205" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2205" t="s">
+        <v>307</v>
+      </c>
+      <c r="C2205" t="s">
+        <v>209</v>
+      </c>
+      <c r="D2205">
+        <v>1952</v>
+      </c>
+      <c r="E2205">
+        <v>17</v>
+      </c>
+      <c r="F2205">
+        <v>147.85</v>
+      </c>
+      <c r="G2205">
+        <v>0</v>
+      </c>
+      <c r="H2205">
+        <v>0</v>
+      </c>
+      <c r="I2205" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2206" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2206" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2206" t="s">
+        <v>307</v>
+      </c>
+      <c r="C2206" t="s">
+        <v>209</v>
+      </c>
+      <c r="D2206">
+        <v>2136</v>
+      </c>
+      <c r="E2206">
+        <v>12</v>
+      </c>
+      <c r="F2206">
+        <v>135.84</v>
+      </c>
+      <c r="G2206">
+        <v>0</v>
+      </c>
+      <c r="H2206">
+        <v>0</v>
+      </c>
+      <c r="I2206" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2207" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2207" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2207" t="s">
+        <v>307</v>
+      </c>
+      <c r="C2207" t="s">
+        <v>209</v>
+      </c>
+      <c r="D2207">
+        <v>1891</v>
+      </c>
+      <c r="E2207">
+        <v>14</v>
+      </c>
+      <c r="F2207">
+        <v>200.39</v>
+      </c>
+      <c r="G2207">
+        <v>0</v>
+      </c>
+      <c r="H2207">
+        <v>0</v>
+      </c>
+      <c r="I2207" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2208" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2208" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2208" t="s">
+        <v>307</v>
+      </c>
+      <c r="C2208" t="s">
+        <v>209</v>
+      </c>
+      <c r="D2208">
+        <v>2298</v>
+      </c>
+      <c r="E2208">
+        <v>16</v>
+      </c>
+      <c r="F2208">
+        <v>186.13</v>
+      </c>
+      <c r="G2208">
+        <v>0</v>
+      </c>
+      <c r="H2208">
+        <v>0</v>
+      </c>
+      <c r="I2208" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2209" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2209" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2209" t="s">
+        <v>308</v>
+      </c>
+      <c r="C2209" t="s">
+        <v>214</v>
+      </c>
+      <c r="D2209">
+        <v>7227</v>
+      </c>
+      <c r="E2209">
+        <v>31</v>
+      </c>
+      <c r="F2209">
+        <v>317.11</v>
+      </c>
+      <c r="G2209">
+        <v>0</v>
+      </c>
+      <c r="H2209">
+        <v>0</v>
+      </c>
+      <c r="I2209" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2210" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2210" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2210" t="s">
+        <v>308</v>
+      </c>
+      <c r="C2210" t="s">
+        <v>214</v>
+      </c>
+      <c r="D2210">
+        <v>8029</v>
+      </c>
+      <c r="E2210">
+        <v>31</v>
+      </c>
+      <c r="F2210">
+        <v>303.57</v>
+      </c>
+      <c r="G2210">
+        <v>1013.56</v>
+      </c>
+      <c r="H2210">
+        <v>1</v>
+      </c>
+      <c r="I2210" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2211" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2211" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2211" t="s">
+        <v>308</v>
+      </c>
+      <c r="C2211" t="s">
+        <v>214</v>
+      </c>
+      <c r="D2211">
+        <v>2968</v>
+      </c>
+      <c r="E2211">
+        <v>10</v>
+      </c>
+      <c r="F2211">
+        <v>107.29</v>
+      </c>
+      <c r="G2211">
+        <v>0</v>
+      </c>
+      <c r="H2211">
+        <v>0</v>
+      </c>
+      <c r="I2211" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2212" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2212" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2212" t="s">
+        <v>308</v>
+      </c>
+      <c r="C2212" t="s">
+        <v>214</v>
+      </c>
+      <c r="D2212">
+        <v>20768</v>
+      </c>
+      <c r="E2212">
+        <v>93</v>
+      </c>
+      <c r="F2212">
+        <v>702.6</v>
+      </c>
+      <c r="G2212">
+        <v>4054.24</v>
+      </c>
+      <c r="H2212">
+        <v>4</v>
+      </c>
+      <c r="I2212" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2213" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2213" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2213" t="s">
+        <v>308</v>
+      </c>
+      <c r="C2213" t="s">
+        <v>214</v>
+      </c>
+      <c r="D2213">
+        <v>30169</v>
+      </c>
+      <c r="E2213">
+        <v>169</v>
+      </c>
+      <c r="F2213">
+        <v>1872.55</v>
+      </c>
+      <c r="G2213">
+        <v>1007.63</v>
+      </c>
+      <c r="H2213">
+        <v>1</v>
+      </c>
+      <c r="I2213" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2214" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2214" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2214" t="s">
+        <v>308</v>
+      </c>
+      <c r="C2214" t="s">
+        <v>214</v>
+      </c>
+      <c r="D2214">
+        <v>3746</v>
+      </c>
+      <c r="E2214">
+        <v>23</v>
+      </c>
+      <c r="F2214">
+        <v>395.24</v>
+      </c>
+      <c r="G2214">
+        <v>0</v>
+      </c>
+      <c r="H2214">
+        <v>0</v>
+      </c>
+      <c r="I2214" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2215" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2215" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2215" t="s">
+        <v>308</v>
+      </c>
+      <c r="C2215" t="s">
+        <v>214</v>
+      </c>
+      <c r="D2215">
+        <v>3933</v>
+      </c>
+      <c r="E2215">
+        <v>16</v>
+      </c>
+      <c r="F2215">
+        <v>233.14</v>
+      </c>
+      <c r="G2215">
+        <v>0</v>
+      </c>
+      <c r="H2215">
+        <v>0</v>
+      </c>
+      <c r="I2215" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2216" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2216" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2216" t="s">
+        <v>309</v>
+      </c>
+      <c r="C2216" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2216">
+        <v>12569</v>
+      </c>
+      <c r="E2216">
+        <v>98</v>
+      </c>
+      <c r="F2216">
+        <v>562.44000000000005</v>
+      </c>
+      <c r="G2216">
+        <v>0</v>
+      </c>
+      <c r="H2216">
+        <v>0</v>
+      </c>
+      <c r="I2216" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2217" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2217" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2217" t="s">
+        <v>309</v>
+      </c>
+      <c r="C2217" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2217">
+        <v>15161</v>
+      </c>
+      <c r="E2217">
+        <v>105</v>
+      </c>
+      <c r="F2217">
+        <v>678.56999999999982</v>
+      </c>
+      <c r="G2217">
+        <v>7244.92</v>
+      </c>
+      <c r="H2217">
+        <v>1</v>
+      </c>
+      <c r="I2217" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2218" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2218" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2218" t="s">
+        <v>309</v>
+      </c>
+      <c r="C2218" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2218">
+        <v>18182</v>
+      </c>
+      <c r="E2218">
+        <v>139</v>
+      </c>
+      <c r="F2218">
+        <v>638.6600000000002</v>
+      </c>
+      <c r="G2218">
+        <v>14489.84</v>
+      </c>
+      <c r="H2218">
+        <v>2</v>
+      </c>
+      <c r="I2218" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2219" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2219" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2219" t="s">
+        <v>309</v>
+      </c>
+      <c r="C2219" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2219">
+        <v>10395</v>
+      </c>
+      <c r="E2219">
+        <v>73</v>
+      </c>
+      <c r="F2219">
+        <v>400.34000000000009</v>
+      </c>
+      <c r="G2219">
+        <v>0</v>
+      </c>
+      <c r="H2219">
+        <v>0</v>
+      </c>
+      <c r="I2219" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2220" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2220" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2220" t="s">
+        <v>309</v>
+      </c>
+      <c r="C2220" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2220">
+        <v>15060</v>
+      </c>
+      <c r="E2220">
+        <v>110</v>
+      </c>
+      <c r="F2220">
+        <v>636.44000000000005</v>
+      </c>
+      <c r="G2220">
+        <v>0</v>
+      </c>
+      <c r="H2220">
+        <v>0</v>
+      </c>
+      <c r="I2220" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2221" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2221" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2221" t="s">
+        <v>309</v>
+      </c>
+      <c r="C2221" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2221">
+        <v>10992</v>
+      </c>
+      <c r="E2221">
+        <v>105</v>
+      </c>
+      <c r="F2221">
+        <v>767.04000000000019</v>
+      </c>
+      <c r="G2221">
+        <v>0</v>
+      </c>
+      <c r="H2221">
+        <v>0</v>
+      </c>
+      <c r="I2221" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2222" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2222" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2222" t="s">
+        <v>309</v>
+      </c>
+      <c r="C2222" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2222">
+        <v>11285</v>
+      </c>
+      <c r="E2222">
+        <v>108</v>
+      </c>
+      <c r="F2222">
+        <v>677.96</v>
+      </c>
+      <c r="G2222">
+        <v>0</v>
+      </c>
+      <c r="H2222">
+        <v>0</v>
+      </c>
+      <c r="I2222" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2223" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2223" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2223" t="s">
+        <v>310</v>
+      </c>
+      <c r="C2223" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2223">
+        <v>7237</v>
+      </c>
+      <c r="E2223">
+        <v>70</v>
+      </c>
+      <c r="F2223">
+        <v>447.97</v>
+      </c>
+      <c r="G2223">
+        <v>0</v>
+      </c>
+      <c r="H2223">
+        <v>0</v>
+      </c>
+      <c r="I2223" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2224" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2224" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2224" t="s">
+        <v>310</v>
+      </c>
+      <c r="C2224" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2224">
+        <v>6381</v>
+      </c>
+      <c r="E2224">
+        <v>64</v>
+      </c>
+      <c r="F2224">
+        <v>459.01</v>
+      </c>
+      <c r="G2224">
+        <v>7244.92</v>
+      </c>
+      <c r="H2224">
+        <v>1</v>
+      </c>
+      <c r="I2224" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2225" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2225" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2225" t="s">
+        <v>310</v>
+      </c>
+      <c r="C2225" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2225">
+        <v>8137</v>
+      </c>
+      <c r="E2225">
+        <v>89</v>
+      </c>
+      <c r="F2225">
+        <v>750.68</v>
+      </c>
+      <c r="G2225">
+        <v>0</v>
+      </c>
+      <c r="H2225">
+        <v>0</v>
+      </c>
+      <c r="I2225" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2226" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2226" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2226" t="s">
+        <v>310</v>
+      </c>
+      <c r="C2226" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2226">
+        <v>7068</v>
+      </c>
+      <c r="E2226">
+        <v>71</v>
+      </c>
+      <c r="F2226">
+        <v>497.15</v>
+      </c>
+      <c r="G2226">
+        <v>0</v>
+      </c>
+      <c r="H2226">
+        <v>0</v>
+      </c>
+      <c r="I2226" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2227" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2227" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2227" t="s">
+        <v>310</v>
+      </c>
+      <c r="C2227" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2227">
+        <v>7452</v>
+      </c>
+      <c r="E2227">
+        <v>79</v>
+      </c>
+      <c r="F2227">
+        <v>635.51</v>
+      </c>
+      <c r="G2227">
+        <v>0</v>
+      </c>
+      <c r="H2227">
+        <v>0</v>
+      </c>
+      <c r="I2227" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2228" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2228" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2228" t="s">
+        <v>310</v>
+      </c>
+      <c r="C2228" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2228">
+        <v>7211</v>
+      </c>
+      <c r="E2228">
+        <v>76</v>
+      </c>
+      <c r="F2228">
+        <v>790.79</v>
+      </c>
+      <c r="G2228">
+        <v>0</v>
+      </c>
+      <c r="H2228">
+        <v>0</v>
+      </c>
+      <c r="I2228" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2229" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2229" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2229" t="s">
+        <v>310</v>
+      </c>
+      <c r="C2229" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2229">
+        <v>7393</v>
+      </c>
+      <c r="E2229">
+        <v>81</v>
+      </c>
+      <c r="F2229">
+        <v>779.99</v>
+      </c>
+      <c r="G2229">
+        <v>27116.11</v>
+      </c>
+      <c r="H2229">
+        <v>3</v>
+      </c>
+      <c r="I2229" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2230" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2230" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2230" t="s">
+        <v>311</v>
+      </c>
+      <c r="C2230" t="s">
+        <v>227</v>
+      </c>
+      <c r="D2230">
+        <v>2231</v>
+      </c>
+      <c r="E2230">
+        <v>9</v>
+      </c>
+      <c r="F2230">
+        <v>68.52</v>
+      </c>
+      <c r="G2230">
+        <v>0</v>
+      </c>
+      <c r="H2230">
+        <v>0</v>
+      </c>
+      <c r="I2230" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2231" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2231" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2231" t="s">
+        <v>311</v>
+      </c>
+      <c r="C2231" t="s">
+        <v>227</v>
+      </c>
+      <c r="D2231">
+        <v>2061</v>
+      </c>
+      <c r="E2231">
+        <v>6</v>
+      </c>
+      <c r="F2231">
+        <v>31.01</v>
+      </c>
+      <c r="G2231">
+        <v>0</v>
+      </c>
+      <c r="H2231">
+        <v>0</v>
+      </c>
+      <c r="I2231" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2232" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2232" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2232" t="s">
+        <v>311</v>
+      </c>
+      <c r="C2232" t="s">
+        <v>227</v>
+      </c>
+      <c r="D2232">
+        <v>2337</v>
+      </c>
+      <c r="E2232">
+        <v>15</v>
+      </c>
+      <c r="F2232">
+        <v>129.13</v>
+      </c>
+      <c r="G2232">
+        <v>0</v>
+      </c>
+      <c r="H2232">
+        <v>0</v>
+      </c>
+      <c r="I2232" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2233" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2233" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2233" t="s">
+        <v>311</v>
+      </c>
+      <c r="C2233" t="s">
+        <v>227</v>
+      </c>
+      <c r="D2233">
+        <v>3149</v>
+      </c>
+      <c r="E2233">
+        <v>7</v>
+      </c>
+      <c r="F2233">
+        <v>64.319999999999993</v>
+      </c>
+      <c r="G2233">
+        <v>0</v>
+      </c>
+      <c r="H2233">
+        <v>0</v>
+      </c>
+      <c r="I2233" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2234" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2234" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2234" t="s">
+        <v>311</v>
+      </c>
+      <c r="C2234" t="s">
+        <v>227</v>
+      </c>
+      <c r="D2234">
+        <v>2153</v>
+      </c>
+      <c r="E2234">
+        <v>7</v>
+      </c>
+      <c r="F2234">
+        <v>64.459999999999994</v>
+      </c>
+      <c r="G2234">
+        <v>0</v>
+      </c>
+      <c r="H2234">
+        <v>0</v>
+      </c>
+      <c r="I2234" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2235" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2235" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2235" t="s">
+        <v>311</v>
+      </c>
+      <c r="C2235" t="s">
+        <v>227</v>
+      </c>
+      <c r="D2235">
+        <v>2767</v>
+      </c>
+      <c r="E2235">
+        <v>7</v>
+      </c>
+      <c r="F2235">
+        <v>90.4</v>
+      </c>
+      <c r="G2235">
+        <v>0</v>
+      </c>
+      <c r="H2235">
+        <v>0</v>
+      </c>
+      <c r="I2235" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2236" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2236" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2236" t="s">
+        <v>311</v>
+      </c>
+      <c r="C2236" t="s">
+        <v>227</v>
+      </c>
+      <c r="D2236">
+        <v>3880</v>
+      </c>
+      <c r="E2236">
+        <v>13</v>
+      </c>
+      <c r="F2236">
+        <v>172.27</v>
+      </c>
+      <c r="G2236">
+        <v>1355.08</v>
+      </c>
+      <c r="H2236">
+        <v>1</v>
+      </c>
+      <c r="I2236" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2237" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2237" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2237" t="s">
+        <v>312</v>
+      </c>
+      <c r="C2237" t="s">
+        <v>226</v>
+      </c>
+      <c r="D2237">
+        <v>1391</v>
+      </c>
+      <c r="E2237">
+        <v>6</v>
+      </c>
+      <c r="F2237">
+        <v>86.72</v>
+      </c>
+      <c r="G2237">
+        <v>0</v>
+      </c>
+      <c r="H2237">
+        <v>0</v>
+      </c>
+      <c r="I2237" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2238" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2238" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2238" t="s">
+        <v>312</v>
+      </c>
+      <c r="C2238" t="s">
+        <v>226</v>
+      </c>
+      <c r="D2238">
+        <v>1128</v>
+      </c>
+      <c r="E2238">
+        <v>10</v>
+      </c>
+      <c r="F2238">
+        <v>128.55000000000001</v>
+      </c>
+      <c r="G2238">
+        <v>0</v>
+      </c>
+      <c r="H2238">
+        <v>0</v>
+      </c>
+      <c r="I2238" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2239" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2239" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2239" t="s">
+        <v>312</v>
+      </c>
+      <c r="C2239" t="s">
+        <v>226</v>
+      </c>
+      <c r="D2239">
+        <v>629</v>
+      </c>
+      <c r="E2239">
+        <v>5</v>
+      </c>
+      <c r="F2239">
+        <v>80.06</v>
+      </c>
+      <c r="G2239">
+        <v>0</v>
+      </c>
+      <c r="H2239">
+        <v>0</v>
+      </c>
+      <c r="I2239" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2240" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2240" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2240" t="s">
+        <v>312</v>
+      </c>
+      <c r="C2240" t="s">
+        <v>226</v>
+      </c>
+      <c r="D2240">
+        <v>1250</v>
+      </c>
+      <c r="E2240">
+        <v>6</v>
+      </c>
+      <c r="F2240">
+        <v>52.21</v>
+      </c>
+      <c r="G2240">
+        <v>0</v>
+      </c>
+      <c r="H2240">
+        <v>0</v>
+      </c>
+      <c r="I2240" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2241" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2241" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2241" t="s">
+        <v>312</v>
+      </c>
+      <c r="C2241" t="s">
+        <v>226</v>
+      </c>
+      <c r="D2241">
+        <v>2167</v>
+      </c>
+      <c r="E2241">
+        <v>11</v>
+      </c>
+      <c r="F2241">
+        <v>145.15</v>
+      </c>
+      <c r="G2241">
+        <v>0</v>
+      </c>
+      <c r="H2241">
+        <v>0</v>
+      </c>
+      <c r="I2241" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2242" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2242" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2242" t="s">
+        <v>312</v>
+      </c>
+      <c r="C2242" t="s">
+        <v>226</v>
+      </c>
+      <c r="D2242">
+        <v>846</v>
+      </c>
+      <c r="E2242">
+        <v>7</v>
+      </c>
+      <c r="F2242">
+        <v>75</v>
+      </c>
+      <c r="G2242">
+        <v>0</v>
+      </c>
+      <c r="H2242">
+        <v>0</v>
+      </c>
+      <c r="I2242" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2243" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2243" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2243" t="s">
+        <v>312</v>
+      </c>
+      <c r="C2243" t="s">
+        <v>226</v>
+      </c>
+      <c r="D2243">
+        <v>900</v>
+      </c>
+      <c r="E2243">
+        <v>6</v>
+      </c>
+      <c r="F2243">
+        <v>76.39</v>
+      </c>
+      <c r="G2243">
+        <v>0</v>
+      </c>
+      <c r="H2243">
+        <v>0</v>
+      </c>
+      <c r="I2243" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2244" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2244" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2244" t="s">
+        <v>313</v>
+      </c>
+      <c r="C2244" t="s">
+        <v>218</v>
+      </c>
+      <c r="D2244">
+        <v>0</v>
+      </c>
+      <c r="E2244">
+        <v>0</v>
+      </c>
+      <c r="F2244">
+        <v>0</v>
+      </c>
+      <c r="G2244">
+        <v>0</v>
+      </c>
+      <c r="H2244">
+        <v>0</v>
+      </c>
+      <c r="I2244" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2245" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2245" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2245" t="s">
+        <v>313</v>
+      </c>
+      <c r="C2245" t="s">
+        <v>218</v>
+      </c>
+      <c r="D2245">
+        <v>0</v>
+      </c>
+      <c r="E2245">
+        <v>0</v>
+      </c>
+      <c r="F2245">
+        <v>0</v>
+      </c>
+      <c r="G2245">
+        <v>0</v>
+      </c>
+      <c r="H2245">
+        <v>0</v>
+      </c>
+      <c r="I2245" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2246" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2246" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2246" t="s">
+        <v>313</v>
+      </c>
+      <c r="C2246" t="s">
+        <v>218</v>
+      </c>
+      <c r="D2246">
+        <v>0</v>
+      </c>
+      <c r="E2246">
+        <v>0</v>
+      </c>
+      <c r="F2246">
+        <v>0</v>
+      </c>
+      <c r="G2246">
+        <v>0</v>
+      </c>
+      <c r="H2246">
+        <v>0</v>
+      </c>
+      <c r="I2246" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2247" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2247" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2247" t="s">
+        <v>313</v>
+      </c>
+      <c r="C2247" t="s">
+        <v>218</v>
+      </c>
+      <c r="D2247">
+        <v>0</v>
+      </c>
+      <c r="E2247">
+        <v>0</v>
+      </c>
+      <c r="F2247">
+        <v>0</v>
+      </c>
+      <c r="G2247">
+        <v>0</v>
+      </c>
+      <c r="H2247">
+        <v>0</v>
+      </c>
+      <c r="I2247" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2248" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2248" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2248" t="s">
+        <v>313</v>
+      </c>
+      <c r="C2248" t="s">
+        <v>218</v>
+      </c>
+      <c r="D2248">
+        <v>0</v>
+      </c>
+      <c r="E2248">
+        <v>0</v>
+      </c>
+      <c r="F2248">
+        <v>0</v>
+      </c>
+      <c r="G2248">
+        <v>0</v>
+      </c>
+      <c r="H2248">
+        <v>0</v>
+      </c>
+      <c r="I2248" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2249" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2249" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2249" t="s">
+        <v>313</v>
+      </c>
+      <c r="C2249" t="s">
+        <v>218</v>
+      </c>
+      <c r="D2249">
+        <v>0</v>
+      </c>
+      <c r="E2249">
+        <v>0</v>
+      </c>
+      <c r="F2249">
+        <v>0</v>
+      </c>
+      <c r="G2249">
+        <v>0</v>
+      </c>
+      <c r="H2249">
+        <v>0</v>
+      </c>
+      <c r="I2249" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2250" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2250" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2250" t="s">
+        <v>313</v>
+      </c>
+      <c r="C2250" t="s">
+        <v>218</v>
+      </c>
+      <c r="D2250">
+        <v>0</v>
+      </c>
+      <c r="E2250">
+        <v>0</v>
+      </c>
+      <c r="F2250">
+        <v>0</v>
+      </c>
+      <c r="G2250">
+        <v>0</v>
+      </c>
+      <c r="H2250">
+        <v>0</v>
+      </c>
+      <c r="I2250" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2251" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2251" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2251" t="s">
+        <v>314</v>
+      </c>
+      <c r="C2251" t="s">
+        <v>242</v>
+      </c>
+      <c r="D2251">
+        <v>3096</v>
+      </c>
+      <c r="E2251">
+        <v>3</v>
+      </c>
+      <c r="F2251">
+        <v>84.19</v>
+      </c>
+      <c r="G2251">
+        <v>0</v>
+      </c>
+      <c r="H2251">
+        <v>0</v>
+      </c>
+      <c r="I2251" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2252" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2252" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2252" t="s">
+        <v>314</v>
+      </c>
+      <c r="C2252" t="s">
+        <v>242</v>
+      </c>
+      <c r="D2252">
+        <v>3397</v>
+      </c>
+      <c r="E2252">
+        <v>0</v>
+      </c>
+      <c r="F2252">
+        <v>0</v>
+      </c>
+      <c r="G2252">
+        <v>0</v>
+      </c>
+      <c r="H2252">
+        <v>0</v>
+      </c>
+      <c r="I2252" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2253" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2253" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2253" t="s">
+        <v>314</v>
+      </c>
+      <c r="C2253" t="s">
+        <v>242</v>
+      </c>
+      <c r="D2253">
+        <v>4299</v>
+      </c>
+      <c r="E2253">
+        <v>6</v>
+      </c>
+      <c r="F2253">
+        <v>59.419999999999995</v>
+      </c>
+      <c r="G2253">
+        <v>0</v>
+      </c>
+      <c r="H2253">
+        <v>0</v>
+      </c>
+      <c r="I2253" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2254" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2254" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2254" t="s">
+        <v>314</v>
+      </c>
+      <c r="C2254" t="s">
+        <v>242</v>
+      </c>
+      <c r="D2254">
+        <v>1810</v>
+      </c>
+      <c r="E2254">
+        <v>2</v>
+      </c>
+      <c r="F2254">
+        <v>30.34</v>
+      </c>
+      <c r="G2254">
+        <v>0</v>
+      </c>
+      <c r="H2254">
+        <v>0</v>
+      </c>
+      <c r="I2254" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2255" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2255" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2255" t="s">
+        <v>314</v>
+      </c>
+      <c r="C2255" t="s">
+        <v>242</v>
+      </c>
+      <c r="D2255">
+        <v>1417</v>
+      </c>
+      <c r="E2255">
+        <v>1</v>
+      </c>
+      <c r="F2255">
+        <v>30.86</v>
+      </c>
+      <c r="G2255">
+        <v>0</v>
+      </c>
+      <c r="H2255">
+        <v>0</v>
+      </c>
+      <c r="I2255" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2256" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2256" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2256" t="s">
+        <v>314</v>
+      </c>
+      <c r="C2256" t="s">
+        <v>242</v>
+      </c>
+      <c r="D2256">
+        <v>3589</v>
+      </c>
+      <c r="E2256">
+        <v>4</v>
+      </c>
+      <c r="F2256">
+        <v>63.13</v>
+      </c>
+      <c r="G2256">
+        <v>0</v>
+      </c>
+      <c r="H2256">
+        <v>0</v>
+      </c>
+      <c r="I2256" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2257" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2257" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2257" t="s">
+        <v>314</v>
+      </c>
+      <c r="C2257" t="s">
+        <v>242</v>
+      </c>
+      <c r="D2257">
+        <v>1951</v>
+      </c>
+      <c r="E2257">
+        <v>5</v>
+      </c>
+      <c r="F2257">
+        <v>32</v>
+      </c>
+      <c r="G2257">
+        <v>0</v>
+      </c>
+      <c r="H2257">
+        <v>0</v>
+      </c>
+      <c r="I2257" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2258" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2258" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2258" t="s">
+        <v>315</v>
+      </c>
+      <c r="C2258" t="s">
+        <v>246</v>
+      </c>
+      <c r="D2258">
+        <v>0</v>
+      </c>
+      <c r="E2258">
+        <v>0</v>
+      </c>
+      <c r="F2258">
+        <v>0</v>
+      </c>
+      <c r="G2258">
+        <v>0</v>
+      </c>
+      <c r="H2258">
+        <v>0</v>
+      </c>
+      <c r="I2258" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2259" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2259" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2259" t="s">
+        <v>315</v>
+      </c>
+      <c r="C2259" t="s">
+        <v>246</v>
+      </c>
+      <c r="D2259">
+        <v>0</v>
+      </c>
+      <c r="E2259">
+        <v>0</v>
+      </c>
+      <c r="F2259">
+        <v>0</v>
+      </c>
+      <c r="G2259">
+        <v>0</v>
+      </c>
+      <c r="H2259">
+        <v>0</v>
+      </c>
+      <c r="I2259" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2260" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2260" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2260" t="s">
+        <v>315</v>
+      </c>
+      <c r="C2260" t="s">
+        <v>246</v>
+      </c>
+      <c r="D2260">
+        <v>0</v>
+      </c>
+      <c r="E2260">
+        <v>0</v>
+      </c>
+      <c r="F2260">
+        <v>0</v>
+      </c>
+      <c r="G2260">
+        <v>0</v>
+      </c>
+      <c r="H2260">
+        <v>0</v>
+      </c>
+      <c r="I2260" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2261" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2261" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2261" t="s">
+        <v>315</v>
+      </c>
+      <c r="C2261" t="s">
+        <v>246</v>
+      </c>
+      <c r="D2261">
+        <v>0</v>
+      </c>
+      <c r="E2261">
+        <v>0</v>
+      </c>
+      <c r="F2261">
+        <v>0</v>
+      </c>
+      <c r="G2261">
+        <v>0</v>
+      </c>
+      <c r="H2261">
+        <v>0</v>
+      </c>
+      <c r="I2261" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2262" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2262" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2262" t="s">
+        <v>315</v>
+      </c>
+      <c r="C2262" t="s">
+        <v>246</v>
+      </c>
+      <c r="D2262">
+        <v>0</v>
+      </c>
+      <c r="E2262">
+        <v>0</v>
+      </c>
+      <c r="F2262">
+        <v>0</v>
+      </c>
+      <c r="G2262">
+        <v>0</v>
+      </c>
+      <c r="H2262">
+        <v>0</v>
+      </c>
+      <c r="I2262" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2263" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2263" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2263" t="s">
+        <v>315</v>
+      </c>
+      <c r="C2263" t="s">
+        <v>246</v>
+      </c>
+      <c r="D2263">
+        <v>0</v>
+      </c>
+      <c r="E2263">
+        <v>0</v>
+      </c>
+      <c r="F2263">
+        <v>0</v>
+      </c>
+      <c r="G2263">
+        <v>0</v>
+      </c>
+      <c r="H2263">
+        <v>0</v>
+      </c>
+      <c r="I2263" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2264" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2264" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2264" t="s">
+        <v>315</v>
+      </c>
+      <c r="C2264" t="s">
+        <v>246</v>
+      </c>
+      <c r="D2264">
+        <v>0</v>
+      </c>
+      <c r="E2264">
+        <v>0</v>
+      </c>
+      <c r="F2264">
+        <v>0</v>
+      </c>
+      <c r="G2264">
+        <v>0</v>
+      </c>
+      <c r="H2264">
+        <v>0</v>
+      </c>
+      <c r="I2264" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2265" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2265" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2265" t="s">
+        <v>316</v>
+      </c>
+      <c r="C2265" t="s">
+        <v>193</v>
+      </c>
+      <c r="D2265">
+        <v>1801</v>
+      </c>
+      <c r="E2265">
+        <v>19</v>
+      </c>
+      <c r="F2265">
+        <v>217.49</v>
+      </c>
+      <c r="G2265">
+        <v>0</v>
+      </c>
+      <c r="H2265">
+        <v>0</v>
+      </c>
+      <c r="I2265" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2266" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2266" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2266" t="s">
+        <v>316</v>
+      </c>
+      <c r="C2266" t="s">
+        <v>193</v>
+      </c>
+      <c r="D2266">
+        <v>5580</v>
+      </c>
+      <c r="E2266">
+        <v>49</v>
+      </c>
+      <c r="F2266">
+        <v>853.97</v>
+      </c>
+      <c r="G2266">
+        <v>0</v>
+      </c>
+      <c r="H2266">
+        <v>0</v>
+      </c>
+      <c r="I2266" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2267" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2267" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2267" t="s">
+        <v>316</v>
+      </c>
+      <c r="C2267" t="s">
+        <v>193</v>
+      </c>
+      <c r="D2267">
+        <v>5447</v>
+      </c>
+      <c r="E2267">
+        <v>36</v>
+      </c>
+      <c r="F2267">
+        <v>431.96</v>
+      </c>
+      <c r="G2267">
+        <v>2981.36</v>
+      </c>
+      <c r="H2267">
+        <v>1</v>
+      </c>
+      <c r="I2267" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2268" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2268" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2268" t="s">
+        <v>316</v>
+      </c>
+      <c r="C2268" t="s">
+        <v>193</v>
+      </c>
+      <c r="D2268">
+        <v>3808</v>
+      </c>
+      <c r="E2268">
+        <v>37</v>
+      </c>
+      <c r="F2268">
+        <v>514.16999999999996</v>
+      </c>
+      <c r="G2268">
+        <v>0</v>
+      </c>
+      <c r="H2268">
+        <v>0</v>
+      </c>
+      <c r="I2268" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2269" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2269" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2269" t="s">
+        <v>316</v>
+      </c>
+      <c r="C2269" t="s">
+        <v>193</v>
+      </c>
+      <c r="D2269">
+        <v>4309</v>
+      </c>
+      <c r="E2269">
+        <v>34</v>
+      </c>
+      <c r="F2269">
+        <v>550.03</v>
+      </c>
+      <c r="G2269">
+        <v>2202.54</v>
+      </c>
+      <c r="H2269">
+        <v>1</v>
+      </c>
+      <c r="I2269" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2270" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2270" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2270" t="s">
+        <v>316</v>
+      </c>
+      <c r="C2270" t="s">
+        <v>193</v>
+      </c>
+      <c r="D2270">
+        <v>3371</v>
+      </c>
+      <c r="E2270">
+        <v>37</v>
+      </c>
+      <c r="F2270">
+        <v>457.29</v>
+      </c>
+      <c r="G2270">
+        <v>4472.04</v>
+      </c>
+      <c r="H2270">
+        <v>2</v>
+      </c>
+      <c r="I2270" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2271" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2271" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2271" t="s">
+        <v>316</v>
+      </c>
+      <c r="C2271" t="s">
+        <v>193</v>
+      </c>
+      <c r="D2271">
+        <v>6095</v>
+      </c>
+      <c r="E2271">
+        <v>54</v>
+      </c>
+      <c r="F2271">
+        <v>748.03</v>
+      </c>
+      <c r="G2271">
+        <v>4377.58</v>
+      </c>
+      <c r="H2271">
+        <v>2</v>
+      </c>
+      <c r="I2271" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2272" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2272" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2272" t="s">
+        <v>318</v>
+      </c>
+      <c r="C2272" t="s">
+        <v>204</v>
+      </c>
+      <c r="D2272">
+        <v>23239.333333333332</v>
+      </c>
+      <c r="E2272">
+        <v>84.666666666666671</v>
+      </c>
+      <c r="F2272">
+        <v>792.17000000000007</v>
+      </c>
+      <c r="G2272">
+        <v>946.89333333333343</v>
+      </c>
+      <c r="H2272">
+        <v>1</v>
+      </c>
+      <c r="I2272" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2273" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2273" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2273" t="s">
+        <v>318</v>
+      </c>
+      <c r="C2273" t="s">
+        <v>223</v>
+      </c>
+      <c r="D2273">
+        <v>23239.333333333332</v>
+      </c>
+      <c r="E2273">
+        <v>84.666666666666671</v>
+      </c>
+      <c r="F2273">
+        <v>792.17000000000007</v>
+      </c>
+      <c r="G2273">
+        <v>946.89333333333343</v>
+      </c>
+      <c r="H2273">
+        <v>1</v>
+      </c>
+      <c r="I2273" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2274" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2274" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2274" t="s">
+        <v>318</v>
+      </c>
+      <c r="C2274" t="s">
+        <v>205</v>
+      </c>
+      <c r="D2274">
+        <v>23239.333333333332</v>
+      </c>
+      <c r="E2274">
+        <v>84.666666666666671</v>
+      </c>
+      <c r="F2274">
+        <v>792.17000000000007</v>
+      </c>
+      <c r="G2274">
+        <v>946.89333333333343</v>
+      </c>
+      <c r="H2274">
+        <v>1</v>
+      </c>
+      <c r="I2274" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2275" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2275" t="s">
+        <v>289</v>
+      </c>
+      <c r="B2275" t="s">
+        <v>317</v>
+      </c>
+      <c r="C2275" t="s">
+        <v>193</v>
+      </c>
+      <c r="D2275">
+        <v>58436.25</v>
+      </c>
+      <c r="E2275">
+        <v>229.375</v>
+      </c>
+      <c r="F2275">
+        <v>2099.8849999999998</v>
+      </c>
+      <c r="G2275">
+        <v>14074.263749999998</v>
+      </c>
+      <c r="H2275">
+        <v>6</v>
+      </c>
+      <c r="I2275" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2276" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2276" t="s">
+        <v>289</v>
+      </c>
+      <c r="B2276" t="s">
+        <v>317</v>
+      </c>
+      <c r="C2276" t="s">
+        <v>227</v>
+      </c>
+      <c r="D2276">
+        <v>58436.25</v>
+      </c>
+      <c r="E2276">
+        <v>229.375</v>
+      </c>
+      <c r="F2276">
+        <v>2099.8849999999998</v>
+      </c>
+      <c r="G2276">
+        <v>14074.263749999998</v>
+      </c>
+      <c r="H2276">
+        <v>6</v>
+      </c>
+      <c r="I2276" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2277" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2277" t="s">
+        <v>289</v>
+      </c>
+      <c r="B2277" t="s">
+        <v>317</v>
+      </c>
+      <c r="C2277" t="s">
+        <v>192</v>
+      </c>
+      <c r="D2277">
+        <v>58436.25</v>
+      </c>
+      <c r="E2277">
+        <v>229.375</v>
+      </c>
+      <c r="F2277">
+        <v>2099.8849999999998</v>
+      </c>
+      <c r="G2277">
+        <v>14074.263749999998</v>
+      </c>
+      <c r="H2277">
+        <v>6</v>
+      </c>
+      <c r="I2277" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2278" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2278" t="s">
+        <v>289</v>
+      </c>
+      <c r="B2278" t="s">
+        <v>317</v>
+      </c>
+      <c r="C2278" t="s">
+        <v>194</v>
+      </c>
+      <c r="D2278">
+        <v>58436.25</v>
+      </c>
+      <c r="E2278">
+        <v>229.375</v>
+      </c>
+      <c r="F2278">
+        <v>2099.8849999999998</v>
+      </c>
+      <c r="G2278">
+        <v>14074.263749999998</v>
+      </c>
+      <c r="H2278">
+        <v>6</v>
+      </c>
+      <c r="I2278" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2279" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2279" t="s">
+        <v>289</v>
+      </c>
+      <c r="B2279" t="s">
+        <v>317</v>
+      </c>
+      <c r="C2279" t="s">
+        <v>215</v>
+      </c>
+      <c r="D2279">
+        <v>58436.25</v>
+      </c>
+      <c r="E2279">
+        <v>229.375</v>
+      </c>
+      <c r="F2279">
+        <v>2099.8849999999998</v>
+      </c>
+      <c r="G2279">
+        <v>14074.263749999998</v>
+      </c>
+      <c r="H2279">
+        <v>6</v>
+      </c>
+      <c r="I2279" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2280" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2280" t="s">
+        <v>289</v>
+      </c>
+      <c r="B2280" t="s">
+        <v>317</v>
+      </c>
+      <c r="C2280" t="s">
+        <v>209</v>
+      </c>
+      <c r="D2280">
+        <v>58436.25</v>
+      </c>
+      <c r="E2280">
+        <v>229.375</v>
+      </c>
+      <c r="F2280">
+        <v>2099.8849999999998</v>
+      </c>
+      <c r="G2280">
+        <v>14074.263749999998</v>
+      </c>
+      <c r="H2280">
+        <v>6</v>
+      </c>
+      <c r="I2280" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2281" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2281" t="s">
+        <v>289</v>
+      </c>
+      <c r="B2281" t="s">
+        <v>317</v>
+      </c>
+      <c r="C2281" t="s">
+        <v>268</v>
+      </c>
+      <c r="D2281">
+        <v>58436.25</v>
+      </c>
+      <c r="E2281">
+        <v>229.375</v>
+      </c>
+      <c r="F2281">
+        <v>2099.8849999999998</v>
+      </c>
+      <c r="G2281">
+        <v>14074.263749999998</v>
+      </c>
+      <c r="H2281">
+        <v>6</v>
+      </c>
+      <c r="I2281" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2282" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2282" t="s">
+        <v>289</v>
+      </c>
+      <c r="B2282" t="s">
+        <v>317</v>
+      </c>
+      <c r="C2282" t="s">
+        <v>230</v>
+      </c>
+      <c r="D2282">
+        <v>58436.25</v>
+      </c>
+      <c r="E2282">
+        <v>229.375</v>
+      </c>
+      <c r="F2282">
+        <v>2099.8849999999998</v>
+      </c>
+      <c r="G2282">
+        <v>14074.263749999998</v>
+      </c>
+      <c r="H2282">
+        <v>6</v>
+      </c>
+      <c r="I2282" t="s">
         <v>302</v>
       </c>
     </row>

--- a/data/ams_weekly_data/Audio_Array/ads_report_week10.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week10.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10805,4 +10806,60 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Portfolio name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Campaign Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Advertised ASIN</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>14 Day Total Sales (₹)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>14 Day Total Units (#)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>